--- a/sheets/대금율보/검수/춤산조 잦은모리.xlsx
+++ b/sheets/대금율보/검수/춤산조 잦은모리.xlsx
@@ -5317,7 +5317,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌇‹</t>
+          <t xml:space="preserve">汰⌇</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -5325,7 +5325,7 @@
         <is>
           <t xml:space="preserve">太
 林
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -5355,19 +5355,19 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳)‹</t>
+          <t xml:space="preserve">湳)</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞)‹</t>
+          <t xml:space="preserve">㳞)</t>
         </is>
       </c>
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞)‹</t>
+          <t xml:space="preserve">㳞)</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -5611,7 +5611,7 @@
       <c r="E10" s="22"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌇‹</t>
+          <t xml:space="preserve">汰⌇</t>
         </is>
       </c>
       <c r="G10" s="22"/>
@@ -5724,7 +5724,7 @@
       <c r="I13" s="22"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南)‹</t>
+          <t xml:space="preserve">南)</t>
         </is>
       </c>
       <c r="K13" s="22"/>
@@ -5864,17 +5864,9 @@
       <c r="C16" s="22"/>
       <c r="D16" s="21"/>
       <c r="E16" s="22"/>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F16" s="21"/>
       <c r="G16" s="22"/>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H16" s="21"/>
       <c r="I16" s="22"/>
       <c r="J16" s="23" t="inlineStr">
         <is>
@@ -5882,11 +5874,7 @@
         </is>
       </c>
       <c r="K16" s="24"/>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L16" s="21"/>
       <c r="M16" s="22"/>
       <c r="N16" s="23" t="inlineStr">
         <is>
@@ -5906,7 +5894,7 @@
         <is>
           <t xml:space="preserve">汰
 淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="S16" s="22"/>

--- a/sheets/대금율보/검수/춤산조 잦은모리.xlsx
+++ b/sheets/대금율보/검수/춤산조 잦은모리.xlsx
@@ -5039,32 +5039,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="229.49" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="229.49" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="229.49" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="229.49" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="229.49" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="229.49" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="229.49" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="229.49" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5672,10 +5672,10 @@
       </c>
       <c r="U10" s="22"/>
     </row>
-    <row r="11">
+    <row r="11" ht="6.0" customHeight="true">
       <c r="A11" s="0"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="102.56" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="229.49" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="229.49" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="229.49" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="229.49" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="229.49" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="229.49" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="229.49" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="229.49" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -6138,7 +6138,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="10" max="16383" man="1"/>
   </rowBreaks>
